--- a/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -820,13 +820,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -820,13 +820,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -820,13 +820,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Scagnetti Giampiero - CR.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -820,13 +820,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
